--- a/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina joue dans le salon. Papa dit : c'est l'heure du dodo. Le corps a besoin de dormir. Nina prend son pyjama bleu. Elle le met. Le pyjama est doux. Papa lit une petite histoire. Nina se couche. Elle dit : dodo. La chambre est calme. Le lendemain, Nina a passé la journée au parc. Le soir revient. Nina a les yeux lourds. Maman dit : c'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama. Elle le met. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Même leçon, autre soir. Nina dit : dodo, maman.</t>
+          <t>Le soir, Nina joue dans le salon. C'est l'heure du dodo. Le corps a besoin de dormir. Nina prend son pyjama bleu. Elle le met. Le pyjama est doux. Papa lit une petite histoire. Nina se couche. Dodo. La chambre est calme. Le lendemain, Nina a passé la journée au parc. Le soir revient. Nina a les yeux lourds. C'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama. Elle le met. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Même leçon, autre soir. Dodo, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nina joue dans le salon.
+papa|C'est l'heure du dodo.
+narrateur|Le corps a besoin de dormir. Nina prend son pyjama bleu. Elle le met. Le pyjama est doux. Papa lit une petite histoire. Nina se couche.
+narrateur|Dodo.
+narrateur|La chambre est calme. Le lendemain, Nina a passé la journée au parc. Le soir revient. Nina a les yeux lourds.
+maman|C'est le soir. On met le pyjama.
+narrateur|Puis c'est le dodo. Nina se souvient. Elle prend le pyjama. Elle le met. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Même leçon, autre soir.
+enfant-f|Dodo, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nina va dormir. Que met-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nina ferme les yeux. La chambre est douce.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 enfant-f|Dodo, maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1514,7 @@
           <t>narrateur|Le soir, Nina va dormir. Que met-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1686,7 @@
           <t>narrateur|Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Nina ferme les yeux. La chambre est douce.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nina met le pyjama, deux soirs</t>
+          <t>Deux soirs, le pyjama bleu</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le plancher est encore tiède du jour. Un soir avec papa, un soir avec maman. Nina met le pyjama bleu. Puis c'est le dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina joue dans le salon. C'est l'heure du dodo. Le corps a besoin de dormir. Nina prend son pyjama bleu. Elle le met. Le pyjama est doux. Papa lit une petite histoire. Nina se couche. Dodo. La chambre est calme. Le lendemain, Nina a passé la journée au parc. Le soir revient. Nina a les yeux lourds. C'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama. Elle le met. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Même leçon, autre soir. Dodo, maman.</t>
+          <t>Le plancher est encore tiède du jour. Le bois garde la chaleur du soleil. Une mite tourne autour de la lampe. Elle fait un petit rond d'or. Ses ailes font un bruit de papier. Le salon sent le bois chaud. Un cube rouge attend sous la table. Nina vit ici, avec papa et maman. Papa, la mite tourne ! Oui. Elle aime la lumière. Le jour a été long. En ce moment, Nina range un cube. Le cube est rouge, un peu rêche. C'est l'heure du dodo. Le corps a besoin de dormir. On met le pyjama ? Oui. Le bleu. Nina prend son pyjama bleu. Le tissu est doux, un peu froissé. Elle le met. Tu as mis le pyjama ? Oui, papa. Bravo, Nina. Papa ouvre le lit. Il lit une petite histoire. Nina se couche. Dodo, papa. Oui. Dodo. La chambre est calme. Le plancher refroidit, tout doux. Le lendemain, le soleil revient. Nina a passé la journée au parc. Le soir revient. La lumière baisse sur les toits. Les chaussures ont un peu de sable. Le sable est chaud, encore. Nina a les yeux lourds. Maman, j'ai du sable. Oui. Le parc reste aux pieds. C'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama bleu. Elle le met encore. Tu t'es souvenue ? Oui. Pyjama, puis dodo. Bravo, Nina. Tu as fait du bon travail. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Dodo, maman. Comme hier soir. Pyjama, puis dodo. La mite n'est plus autour de la lampe. Le plancher est frais, maintenant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,19 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nina joue dans le salon.
+          <t>narrateur|Le plancher est encore tiède du jour.
+narrateur|Le bois garde la chaleur du soleil.
+narrateur|Une mite tourne autour de la lampe.
+narrateur|Elle fait un petit rond d'or.
+narrateur|Ses ailes font un bruit de papier.
+narrateur|Le salon sent le bois chaud.
+narrateur|Un cube rouge attend sous la table.
+narrateur|Nina vit ici, avec papa et maman.
+enfant-f|Papa, la mite tourne !
+papa|Oui.
+papa|Elle aime la lumière.
+maman|Le jour a été long.
+narrateur|En ce moment, Nina range un cube.
+narrateur|Le cube est rouge, un peu rêche.
 papa|C'est l'heure du dodo.
-narrateur|Le corps a besoin de dormir. Nina prend son pyjama bleu. Elle le met. Le pyjama est doux. Papa lit une petite histoire. Nina se couche.
-narrateur|Dodo.
-narrateur|La chambre est calme. Le lendemain, Nina a passé la journée au parc. Le soir revient. Nina a les yeux lourds.
-maman|C'est le soir. On met le pyjama.
-narrateur|Puis c'est le dodo. Nina se souvient. Elle prend le pyjama. Elle le met. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Même leçon, autre soir.
-enfant-f|Dodo, maman.</t>
+papa|Le corps a besoin de dormir.
+maman|On met le pyjama ?
+enfant-f|Oui.
+enfant-f|Le bleu.
+narrateur|Nina prend son pyjama bleu.
+narrateur|Le tissu est doux, un peu froissé.
+narrateur|Elle le met.
+papa|Tu as mis le pyjama ?
+enfant-f|Oui, papa.
+papa|Bravo, Nina.
+narrateur|Papa ouvre le lit.
+narrateur|Il lit une petite histoire.
+narrateur|Nina se couche.
+enfant-f|Dodo, papa.
+papa|Oui.
+papa|Dodo.
+narrateur|La chambre est calme.
+narrateur|Le plancher refroidit, tout doux.
+narrateur|Le lendemain, le soleil revient.
+narrateur|Nina a passé la journée au parc.
+narrateur|Le soir revient.
+narrateur|La lumière baisse sur les toits.
+narrateur|Les chaussures ont un peu de sable.
+narrateur|Le sable est chaud, encore.
+narrateur|Nina a les yeux lourds.
+enfant-f|Maman, j'ai du sable.
+maman|Oui.
+maman|Le parc reste aux pieds.
+maman|C'est le soir.
+maman|On met le pyjama.
+narrateur|Puis c'est le dodo.
+narrateur|Nina se souvient.
+narrateur|Elle prend le pyjama bleu.
+narrateur|Elle le met encore.
+maman|Tu t'es souvenue ?
+enfant-f|Oui.
+enfant-f|Pyjama, puis dodo.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+narrateur|Maman raconte une histoire.
+narrateur|Nina se couche.
+narrateur|Le corps a besoin de dormir.
+enfant-f|Dodo, maman.
+papa|Comme hier soir.
+maman|Pyjama, puis dodo.
+narrateur|La mite n'est plus autour de la lampe.
+narrateur|Le plancher est frais, maintenant.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>lampe,plancher</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nina va dormir. Que met-elle ?</t>
+          <t>narrateur|Le soir, Nina va dormir.
+narrateur|Que met-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1539,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo.</t>
+          <t>Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo. Tu as mis le pyjama, les deux soirs ? Oui. Le pyjama. Bravo, Nina. Tu as fait du bon travail. Le pyjama bleu repose au bord du lit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,7 +1750,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo.</t>
+          <t>narrateur|Nina a mis le pyjama.
+narrateur|Un soir avec papa.
+narrateur|Un soir avec maman.
+narrateur|Puis dodo.
+maman|Tu as mis le pyjama, les deux soirs ?
+enfant-f|Oui.
+enfant-f|Le pyjama.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le pyjama bleu repose au bord du lit.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1711,7 +1787,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina ferme les yeux. La chambre est douce.</t>
+          <t>Nina ferme les yeux. La chambre est douce. Le pyjama bleu sent encore le savon. Tu es bien au lit ? Oui, maman. Bonne nuit, Nina. Bonne nuit. Bravo. Le sable n'est plus aux chaussures. Les chaussures sèchent près de la porte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,7 +1923,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nina ferme les yeux. La chambre est douce.</t>
+          <t>narrateur|Nina ferme les yeux.
+narrateur|La chambre est douce.
+narrateur|Le pyjama bleu sent encore le savon.
+maman|Tu es bien au lit ?
+enfant-f|Oui, maman.
+papa|Bonne nuit, Nina.
+enfant-f|Bonne nuit.
+maman|Bravo.
+narrateur|Le sable n'est plus aux chaussures.
+narrateur|Les chaussures sèchent près de la porte.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1875,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Deux soirs, j'ai mis le pyjama. Puis dodo. Bravo. Tu as fait du bon travail. Le plancher est calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Deux soirs, j'ai mis le pyjama.
+enfant-f|Puis dodo.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le plancher est calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le plancher est encore tiède du jour. Le bois garde la chaleur du soleil. Une mite tourne autour de la lampe. Elle fait un petit rond d'or. Ses ailes font un bruit de papier. Le salon sent le bois chaud. Un cube rouge attend sous la table. Nina vit ici, avec papa et maman. Papa, la mite tourne ! Oui. Elle aime la lumière. Le jour a été long. En ce moment, Nina range un cube. Le cube est rouge, un peu rêche. C'est l'heure du dodo. Le corps a besoin de dormir. On met le pyjama ? Oui. Le bleu. Nina prend son pyjama bleu. Le tissu est doux, un peu froissé. Elle le met. Tu as mis le pyjama ? Oui, papa. Bravo, Nina. Papa ouvre le lit. Il lit une petite histoire. Nina se couche. Dodo, papa. Oui. Dodo. La chambre est calme. Le plancher refroidit, tout doux. Le lendemain, le soleil revient. Nina a passé la journée au parc. Le soir revient. La lumière baisse sur les toits. Les chaussures ont un peu de sable. Le sable est chaud, encore. Nina a les yeux lourds. Maman, j'ai du sable. Oui. Le parc reste aux pieds. C'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama bleu. Elle le met encore. Tu t'es souvenue ? Oui. Pyjama, puis dodo. Bravo, Nina. Tu as fait du bon travail. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Dodo, maman. Comme hier soir. Pyjama, puis dodo. La mite n'est plus autour de la lampe. Le plancher est frais, maintenant.</t>
+          <t>Le plancher est encore tiède du jour. Le bois garde la chaleur du soleil. Une mite tourne autour de la lampe. Elle fait un petit rond d'or. Ses ailes font un bruit de papier. Le salon sent le bois chaud. Un cube rouge attend sous la table. Nina vit ici, avec papa et maman. Papa, la mite tourne ! Oui. Elle aime la lumière. Le jour a été long. En ce moment, Nina range un cube. Le cube est rouge, un peu rêche. C'est l'heure du dodo. Le corps a besoin de dormir. On met le pyjama ? Oui. Le bleu. Nina prend son pyjama bleu. Le tissu est doux, un peu froissé. Elle le met. Tu as mis le pyjama ? Oui, papa. Bravo, Nina. Papa ouvre le lit. Il lit une petite histoire. Nina se couche. Dodo, papa. Oui. Dodo. La chambre est calme. Le plancher refroidit, tout doux. Le lendemain, le soleil revient. Nina a passé la journée au parc. Le soir revient. La lumière baisse sur les toits. Les chaussures ont un peu de sable. Le sable est chaud, encore. Nina a les yeux lourds. Maman, j'ai du sable. Oui. Le parc reste aux pieds. C'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama bleu. Elle le met encore. Tu t'es souvenue ? Oui. Pyjama, puis dodo. Bravo, Nina. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Dodo, maman. Comme hier soir. Pyjama, puis dodo. La mite n'est plus autour de la lampe. Le plancher est frais, maintenant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, Nina joue dans le salon. Papa dit : c'est l'heure du dodo. Le corps a besoin de dormir. Nina prend son pyjama bleu. Elle le met. Le pyjama est doux. Papa lit une petite histoire. Nina se couche. Elle dit : dodo. La chambre est calme. Le lendemain, Nina a passé la journée au parc. Le soir revient. Nina a les yeux lourds. Maman dit : c'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama. Elle le met. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Même leçon, autre soir. Nina dit : dodo, maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le plancher est encore tiède du jour. Le bois garde la chaleur du soleil. Une mite tourne autour de la lampe. Elle fait un petit rond d'or. Ses ailes font un bruit de papier. Le salon sent le bois chaud. Un cube rouge attend sous la table. Nina vit ici, avec papa et maman. Papa, la mite tourne ! Oui. Elle aime la lumière. Le jour a été long. En ce moment, Nina range un cube. Le cube est rouge, un peu rêche. C'est l'heure du dodo. Le corps a besoin de dormir. On met le pyjama ? Oui. Le bleu. Nina prend son pyjama bleu. Le tissu est doux, un peu froissé. Elle le met. Tu as mis le pyjama ? Oui, papa. Bravo, Nina. Papa ouvre le lit. Il lit une petite histoire. Nina se couche. Dodo, papa. Oui. Dodo. La chambre est calme. Le plancher refroidit, tout doux. Le lendemain, le soleil revient. Nina a passé la journée au parc. Le soir revient. La lumière baisse sur les toits. Les chaussures ont un peu de sable. Le sable est chaud, encore. Nina a les yeux lourds. Maman, j'ai du sable. Oui. Le parc reste aux pieds. C'est le soir. On met le pyjama. Puis c'est le dodo. Nina se souvient. Elle prend le pyjama bleu. Elle le met encore. Tu t'es souvenue ? Oui. Pyjama, puis dodo. Bravo, Nina. Maman raconte une histoire. Nina se couche. Le corps a besoin de dormir. Dodo, maman. Comme hier soir. Pyjama, puis dodo. La mite n'est plus autour de la lampe. Le plancher est frais, maintenant.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 enfant-f|Oui.
 enfant-f|Pyjama, puis dodo.
 maman|Bravo, Nina.
-maman|Tu as fait du bon travail.
 narrateur|Maman raconte une histoire.
 narrateur|Nina se couche.
 narrateur|Le corps a besoin de dormir.
@@ -1422,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, Nina va dormir. Que met-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir, Nina va dormir. Que met-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1581,7 +1580,6 @@
 narrateur|Que met-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo. Tu as mis le pyjama, les deux soirs ? Oui. Le pyjama. Bravo, Nina. Tu as fait du bon travail. Le pyjama bleu repose au bord du lit.</t>
+          <t>Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo. Tu as mis le pyjama, les deux soirs ? Oui. Le pyjama. Bravo, Nina. Le pyjama bleu repose au bord du lit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina a mis le pyjama. Un &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt; avec papa. Un soir avec maman. Puis dodo.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a mis le pyjama. Un soir avec papa. Un soir avec maman. Puis dodo. Tu as mis le pyjama, les deux soirs ? Oui. Le pyjama. Bravo, Nina. Le pyjama bleu repose au bord du lit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1758,11 +1756,9 @@
 enfant-f|Oui.
 enfant-f|Le pyjama.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
 narrateur|Le pyjama bleu repose au bord du lit.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,7 +1788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina ferme les yeux. La chambre est douce.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina ferme les yeux. La chambre est douce. Le pyjama bleu sent encore le savon. Tu es bien au lit ? Oui, maman. Bonne nuit, Nina. Bonne nuit. Bravo. Le sable n'est plus aux chaussures. Les chaussures sèchent près de la porte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1931,6 @@
 narrateur|Les chaussures sèchent près de la porte.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Deux soirs, j'ai mis le pyjama. Puis dodo. Bravo. Tu as fait du bon travail. Le plancher est calme. L'histoire est finie.</t>
+          <t>Deux soirs, j'ai mis le pyjama. Puis dodo. Bravo. Le plancher est calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Deux soirs, j'ai mis le pyjama. Puis dodo. Bravo. Le plancher est calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
           <t>enfant-f|Deux soirs, j'ai mis le pyjama.
 enfant-f|Puis dodo.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le plancher est calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le plancher est calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>
